--- a/erp/templates/fire-plan-workbook.xlsx
+++ b/erp/templates/fire-plan-workbook.xlsx
@@ -3933,7 +3933,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">☐ 매월 (   1   일)</t>
+          <t xml:space="preserve">☐ 매월 (       일)</t>
         </is>
       </c>
       <c r="G17" s="7"/>
@@ -6853,7 +6853,7 @@
     <row r="3" ht="27.0" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">[   25 년 제  1 차] 소방훈련 · 교육 및 자체평가 계획</t>
+          <t xml:space="preserve">[      년 제    차] 소방훈련 · 교육 및 자체평가 계획</t>
         </is>
       </c>
       <c r="B3" s="30"/>
@@ -9968,7 +9968,7 @@
       <c r="I17" s="59"/>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> □ 기타(  상시 부착        )</t>
+          <t xml:space="preserve"> □ 기타(               )</t>
         </is>
       </c>
       <c r="K17" s="9"/>
@@ -11000,7 +11000,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100명</t>
+          <t xml:space="preserve">명</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">□ 기타 (   옥상       )</t>
+          <t xml:space="preserve">□ 기타 (            )</t>
         </is>
       </c>
       <c r="D11" s="7"/>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 개소</t>
+          <t xml:space="preserve">개소</t>
         </is>
       </c>
       <c r="K13" s="7"/>
